--- a/Tennis/postplanner-imports/tfr-postplanner-2026-05-05.xlsx
+++ b/Tennis/postplanner-imports/tfr-postplanner-2026-05-05.xlsx
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05/05/2026  12:43</t>
+          <t>05/05/2026  08:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05/05/2026  13:52</t>
+          <t>05/05/2026  10:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05/05/2026  15:01</t>
+          <t>05/05/2026  12:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05/05/2026  16:10</t>
+          <t>05/05/2026  12:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05/05/2026  17:19</t>
+          <t>05/05/2026  15:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/05/2026  18:28</t>
+          <t>05/05/2026  18:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/05/2026  19:37</t>
+          <t>05/05/2026  18:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/05/2026  20:46</t>
+          <t>05/05/2026  21:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
